--- a/اعضاء-تجريبيون-SCVA.xlsx
+++ b/اعضاء-تجريبيون-SCVA.xlsx
@@ -398,23 +398,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O101"/>
-  <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" customWidth="1"/>
-    <col min="9" max="9" width="28.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="32.83203125" customWidth="1"/>
-    <col min="13" max="13" width="14.83203125" customWidth="1"/>
-    <col min="14" max="14" width="14.83203125" customWidth="1"/>
-    <col min="15" max="15" width="18.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2049,7 +2032,7 @@
         <v>السويداء</v>
       </c>
       <c r="L35" t="str">
-        <v>مستشفى الأسد الجامعي - السويداء</v>
+        <v>مستشفى الجمهوري الجامعي - السويداء</v>
       </c>
       <c r="M35" t="str">
         <v>2007-10-01</v>
@@ -2096,7 +2079,7 @@
         <v>درعا</v>
       </c>
       <c r="L36" t="str">
-        <v>مستشفى الأسد الجامعي - درعا</v>
+        <v>مستشفى الجمهوري الجامعي - درعا</v>
       </c>
       <c r="M36" t="str">
         <v>2004-12-01</v>
